--- a/assessment_forms/045_locomotive_operation_knowledge_assessment--assessment_forms.xlsx
+++ b/assessment_forms/045_locomotive_operation_knowledge_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'engineer',_'label':_'engineer'}</t>
+          <t>engineer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Engineer', 'label': 'Engineer'}</t>
+          <t>Engineer</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'conductor',_'label':_'conductor'}</t>
+          <t>conductor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Conductor', 'label': 'Conductor'}</t>
+          <t>Conductor</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'brake_systems',_'label':_'brake_systems'}</t>
+          <t>brake_systems</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Brake Systems', 'label': 'Brake Systems'}</t>
+          <t>Brake Systems</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'signaling_and_communication',_'label':_'signaling_and_communication'}</t>
+          <t>signaling_and_communication</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Signaling and Communication', 'label': 'Signaling and Communication'}</t>
+          <t>Signaling and Communication</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'locomotive_controls',_'label':_'locomotive_controls'}</t>
+          <t>locomotive_controls</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Locomotive Controls', 'label': 'Locomotive Controls'}</t>
+          <t>Locomotive Controls</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'operator_1',_'label':_'operator_1'}</t>
+          <t>operator_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Operator 1', 'label': 'Operator 1'}</t>
+          <t>Operator 1</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'operator_2',_'label':_'operator_2'}</t>
+          <t>operator_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Operator 2', 'label': 'Operator 2'}</t>
+          <t>Operator 2</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'diesel',_'label':_'diesel'}</t>
+          <t>diesel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Diesel', 'label': 'Diesel'}</t>
+          <t>Diesel</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'electric',_'label':_'electric'}</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Electric', 'label': 'Electric'}</t>
+          <t>Electric</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'hydraulic',_'label':_'hydraulic'}</t>
+          <t>hydraulic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Hydraulic', 'label': 'Hydraulic'}</t>
+          <t>Hydraulic</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'manager',_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Manager', 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'operator',_'label':_'operator'}</t>
+          <t>operator</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Operator', 'label': 'Operator'}</t>
+          <t>Operator</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'trainer',_'label':_'trainer'}</t>
+          <t>trainer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Trainer', 'label': 'Trainer'}</t>
+          <t>Trainer</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'approved',_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Approved', 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'rejected',_'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Rejected', 'label': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'operator_1',_'label':_'operator_1'}</t>
+          <t>operator_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Operator 1', 'label': 'Operator 1'}</t>
+          <t>Operator 1</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'operator_2',_'label':_'operator_2'}</t>
+          <t>operator_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Operator 2', 'label': 'Operator 2'}</t>
+          <t>Operator 2</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'manager',_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Manager', 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'operator',_'label':_'operator'}</t>
+          <t>operator</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Operator', 'label': 'Operator'}</t>
+          <t>Operator</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'trainer',_'label':_'trainer'}</t>
+          <t>trainer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Trainer', 'label': 'Trainer'}</t>
+          <t>Trainer</t>
         </is>
       </c>
     </row>
